--- a/examples/advanced_output.xlsx
+++ b/examples/advanced_output.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0원"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,13 +33,26 @@
       <sz val="16"/>
     </font>
     <font>
+      <color rgb="00FF6600"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <color rgb="00CCCCCC"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
     </font>
   </fonts>
   <fills count="5">
@@ -84,22 +97,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,14 +482,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,7 +518,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>부제: 부제 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -507,13 +533,20 @@
               <color rgb="002E75B6"/>
               <sz val="14"/>
             </rPr>
-            <t>📁 개발팀</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
+            <t>📁 1. 개발팀</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>⭐ 첫 번째 부서입니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">설명: </t>
@@ -528,87 +561,122 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>직책</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>급여</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>김</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> 철수</t>
-          </r>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>시니어 개발자</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>재직</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>이</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> 영희</t>
-          </r>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>주니어 개발자</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>재직</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>직원 수: 3명</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>✅ 활성 부서 (직원 있음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>직책</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>급여</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>김</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> 철수</t>
+          </r>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>시니어 개발자</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>✅ 재직</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>이</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> 영희</t>
+          </r>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>주니어 개발자</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>✅ 재직</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <b val="1"/>
@@ -620,22 +688,23 @@
           </r>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>테크 리드</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="E12" s="8" t="n">
         <v>9000000</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>재직</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>✅ 재직</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">총 </t>
@@ -660,9 +729,15 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -670,35 +745,62 @@
               <color rgb="002E75B6"/>
               <sz val="14"/>
             </rPr>
-            <t>📁 기획팀</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+            <t>📁 2. 기획팀</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>직원 수: 2명</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>✅ 활성 부서 (직원 있음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>직책</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>급여</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -711,22 +813,26 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="E19" s="8" t="n">
         <v>6500000</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>재직</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>✅ 재직</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -739,22 +845,23 @@
           </r>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>기획자</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="E20" s="8" t="n">
         <v>5000000</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>휴직</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>⏸️ 휴직</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">총 </t>
@@ -779,9 +886,15 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="2" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -789,13 +902,13 @@
               <color rgb="002E75B6"/>
               <sz val="14"/>
             </rPr>
-            <t>📁 디자인팀</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
+            <t>📁 3. 디자인팀</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">설명: </t>
@@ -810,30 +923,57 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>직원 수: 1명</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>✅ 활성 부서 (직원 있음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>직책</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>급여</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -846,22 +986,23 @@
           </r>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>UI 디자이너</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="E28" s="8" t="n">
         <v>5500000</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>재직</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>✅ 재직</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">총 </t>
@@ -881,20 +1022,26 @@
               <b val="1"/>
               <color rgb="002E75B6"/>
             </rPr>
-            <t>5,500,000원</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="8">
+            <t>계산 중</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11">
         <f>== 전체 요약 ===</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>부서 목록: 개발팀, 기획팀, 디자인팀</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">전체 직원: </t>
@@ -908,8 +1055,25 @@
             <t>6</t>
           </r>
           <r>
-            <t>명</t>
-          </r>
+            <t xml:space="preserve">명 (총 </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002E75B6"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <t>개 부서)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>📋 이 리포트는 자동 생성되었습니다.</t>
         </is>
       </c>
     </row>

--- a/examples/advanced_output.xlsx
+++ b/examples/advanced_output.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1077,6 +1077,96 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="11">
+        <f>== 새 필터 테스트 ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>upper: HELLO WORLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>lower: hello world</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>title: Hello World Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>trim: [trimmed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>replace: hello Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>round: 3.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>abs: 42</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>int: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>float: 123.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>first: apple</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>last: cherry</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>chained: TRIMMED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
